--- a/plan/Plan.xlsx
+++ b/plan/Plan.xlsx
@@ -8,16 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C8DEC09-2595-4BDB-84C3-49A9B5A7681F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BAA379-E9D5-4449-87B5-C35C6C2EAB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-2652" yWindow="1344" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="1" r:id="rId1"/>
     <sheet name="Plan" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
   <si>
     <t>No</t>
   </si>
@@ -207,6 +206,15 @@
   </si>
   <si>
     <t>Nguyen Chung Văn</t>
+  </si>
+  <si>
+    <t>Nguyen Cong Hưởng</t>
+  </si>
+  <si>
+    <t>nconghuong1401@gmail.com</t>
+  </si>
+  <si>
+    <t>0976494199</t>
   </si>
 </sst>
 </file>
@@ -297,7 +305,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -370,12 +378,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -411,8 +430,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -698,16 +726,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J1048548"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="5" max="5" width="11.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" customWidth="1"/>
+    <col min="3" max="3" width="30.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" customWidth="1"/>
+    <col min="7" max="7" width="1.6640625" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -746,7 +775,7 @@
       <c r="A2" s="18">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C2" s="25" t="s">
@@ -995,24 +1024,54 @@
       </c>
     </row>
     <row r="10" spans="1:10" s="11" customFormat="1">
-      <c r="A10" s="18">
+      <c r="A10" s="28">
         <v>9</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="8" t="s">
         <v>23</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="10"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+    </row>
+    <row r="11" spans="1:10" s="11" customFormat="1">
+      <c r="A11" s="18">
+        <v>10</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="3">
+        <v>4</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="1048541" spans="4:5">
       <c r="D1048541" s="1"/>
@@ -1050,6 +1109,7 @@
     <hyperlink ref="C6" r:id="rId5" xr:uid="{25C23E2D-FFF4-458F-9045-201675A593D6}"/>
     <hyperlink ref="C8" r:id="rId6" xr:uid="{0CB78E6A-0CE2-4B67-948B-3C0C01A6A31F}"/>
     <hyperlink ref="C9" r:id="rId7" xr:uid="{EFA9FC9B-A569-4211-9DFD-6EAB9ABE2662}"/>
+    <hyperlink ref="C11" r:id="rId8" xr:uid="{B1543FEB-2824-491A-B650-18B8CEE94521}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1058,11 +1118,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EBF7271-440B-437E-A715-AB16B6C4BC2C}">
   <dimension ref="A1:W18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23">
@@ -1132,32 +1192,32 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="17"/>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="36" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="36"/>
+      <c r="F2" s="36"/>
+      <c r="G2" s="36"/>
+      <c r="H2" s="36"/>
+      <c r="I2" s="36"/>
+      <c r="J2" s="36"/>
+      <c r="K2" s="36"/>
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="36" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="29"/>
-      <c r="P2" s="29"/>
-      <c r="Q2" s="29"/>
-      <c r="R2" s="29"/>
-      <c r="S2" s="29"/>
-      <c r="T2" s="29"/>
-      <c r="U2" s="29"/>
-      <c r="V2" s="29"/>
-      <c r="W2" s="29"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="36"/>
+      <c r="Q2" s="36"/>
+      <c r="R2" s="36"/>
+      <c r="S2" s="36"/>
+      <c r="T2" s="36"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="36"/>
+      <c r="W2" s="36"/>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="17" t="s">

--- a/plan/Plan.xlsx
+++ b/plan/Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70BAA379-E9D5-4449-87B5-C35C6C2EAB8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF3BAF3-892F-43CF-AA23-8B7E36F21E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2652" yWindow="1344" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
   <si>
     <t>No</t>
   </si>
@@ -215,6 +215,12 @@
   </si>
   <si>
     <t>0976494199</t>
+  </si>
+  <si>
+    <t>Lê phạm minh hiếu</t>
+  </si>
+  <si>
+    <t>ĐH Thành Đô</t>
   </si>
 </sst>
 </file>
@@ -305,7 +311,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -389,12 +395,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -441,6 +458,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -733,7 +751,7 @@
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="11.5546875" customWidth="1"/>
     <col min="6" max="6" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="1.6640625" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" customWidth="1"/>
     <col min="8" max="8" width="8" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="36.6640625" bestFit="1" customWidth="1"/>
@@ -1071,6 +1089,14 @@
       <c r="I11" s="3"/>
       <c r="J11" s="3" t="s">
         <v>44</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12" t="s">
+        <v>63</v>
+      </c>
+      <c r="J12" s="36" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="1048541" spans="4:5">
@@ -1192,32 +1218,32 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="17"/>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
-      <c r="J2" s="36"/>
-      <c r="K2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
-      <c r="N2" s="36" t="s">
+      <c r="N2" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="36"/>
-      <c r="P2" s="36"/>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="36"/>
-      <c r="S2" s="36"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="36"/>
+      <c r="O2" s="37"/>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="17" t="s">

--- a/plan/Plan.xlsx
+++ b/plan/Plan.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CF3BAF3-892F-43CF-AA23-8B7E36F21E94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4168823-4508-4753-9BA4-BEF93AD38454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="1" r:id="rId1"/>
     <sheet name="Plan" sheetId="2" r:id="rId2"/>
+    <sheet name="Plan-Coding" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
   <si>
     <t>No</t>
   </si>
@@ -221,6 +222,60 @@
   </si>
   <si>
     <t>ĐH Thành Đô</t>
+  </si>
+  <si>
+    <t>Sprint 3 - 3/3 - 14/3</t>
+  </si>
+  <si>
+    <t>Sprint 4 - 17/03 - 28/3</t>
+  </si>
+  <si>
+    <t>User service</t>
+  </si>
+  <si>
+    <t>Search</t>
+  </si>
+  <si>
+    <t>Common exception</t>
+  </si>
+  <si>
+    <t>PIC</t>
+  </si>
+  <si>
+    <t>Dũng</t>
+  </si>
+  <si>
+    <t>Hưởng</t>
+  </si>
+  <si>
+    <t>Nam</t>
+  </si>
+  <si>
+    <t>Tuấn Anh</t>
+  </si>
+  <si>
+    <t>Phúc</t>
+  </si>
+  <si>
+    <t>Văn</t>
+  </si>
+  <si>
+    <t>Detail screen/delete</t>
+  </si>
+  <si>
+    <t>Create/update</t>
+  </si>
+  <si>
+    <t>Thái</t>
+  </si>
+  <si>
+    <t>Import (excel and csv)</t>
+  </si>
+  <si>
+    <t>Export (excel and csv)</t>
+  </si>
+  <si>
+    <t>Common (message_en/vn, validation)</t>
   </si>
 </sst>
 </file>
@@ -267,7 +322,7 @@
       <name val="TimesNewRomanPSMT"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -307,6 +362,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -411,7 +472,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -462,6 +523,7 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1654,4 +1716,595 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43DE5D9-EEEF-4F18-8F47-33166F5D148C}">
+  <dimension ref="A1:X19"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.33203125" customWidth="1"/>
+    <col min="3" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" s="17"/>
+      <c r="B1" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="37" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
+      <c r="H2" s="37"/>
+      <c r="I2" s="37"/>
+      <c r="J2" s="37"/>
+      <c r="K2" s="37"/>
+      <c r="L2" s="37"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="P2" s="37"/>
+      <c r="Q2" s="37"/>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="37"/>
+      <c r="X2" s="37"/>
+    </row>
+    <row r="3" spans="1:24">
+      <c r="A3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
+      <c r="V3" s="17"/>
+      <c r="W3" s="17"/>
+      <c r="X3" s="17"/>
+    </row>
+    <row r="4" spans="1:24">
+      <c r="A4" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="17"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="17"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="17"/>
+      <c r="R4" s="17"/>
+      <c r="S4" s="17"/>
+      <c r="T4" s="17"/>
+      <c r="U4" s="17"/>
+      <c r="V4" s="17"/>
+      <c r="W4" s="17"/>
+      <c r="X4" s="17"/>
+    </row>
+    <row r="5" spans="1:24">
+      <c r="A5" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="17"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
+      <c r="Q5" s="7"/>
+      <c r="R5" s="7"/>
+      <c r="S5" s="7"/>
+      <c r="T5" s="7"/>
+      <c r="U5" s="7"/>
+      <c r="V5" s="7"/>
+      <c r="W5" s="7"/>
+      <c r="X5" s="7"/>
+    </row>
+    <row r="6" spans="1:24">
+      <c r="A6" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
+      <c r="M6" s="16"/>
+      <c r="N6" s="16"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7"/>
+      <c r="Q6" s="7"/>
+      <c r="R6" s="7"/>
+      <c r="S6" s="7"/>
+      <c r="T6" s="7"/>
+      <c r="U6" s="7"/>
+      <c r="V6" s="7"/>
+      <c r="W6" s="7"/>
+      <c r="X6" s="7"/>
+    </row>
+    <row r="7" spans="1:24">
+      <c r="A7" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="17"/>
+      <c r="L7" s="17"/>
+      <c r="M7" s="16"/>
+      <c r="N7" s="16"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+      <c r="S7" s="7"/>
+      <c r="T7" s="7"/>
+      <c r="U7" s="7"/>
+      <c r="V7" s="7"/>
+      <c r="W7" s="7"/>
+      <c r="X7" s="7"/>
+    </row>
+    <row r="8" spans="1:24">
+      <c r="A8" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="17"/>
+      <c r="D8" s="17"/>
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="17"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="17"/>
+      <c r="L8" s="17"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+      <c r="S8" s="7"/>
+      <c r="T8" s="7"/>
+      <c r="U8" s="7"/>
+      <c r="V8" s="7"/>
+      <c r="W8" s="7"/>
+      <c r="X8" s="7"/>
+    </row>
+    <row r="9" spans="1:24">
+      <c r="A9" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="17"/>
+      <c r="D9" s="17"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="17"/>
+      <c r="L9" s="17"/>
+      <c r="M9" s="16"/>
+      <c r="N9" s="16"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+      <c r="S9" s="7"/>
+      <c r="T9" s="7"/>
+      <c r="U9" s="7"/>
+      <c r="V9" s="7"/>
+      <c r="W9" s="7"/>
+      <c r="X9" s="7"/>
+    </row>
+    <row r="10" spans="1:24">
+      <c r="A10" s="17"/>
+      <c r="B10" s="17"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="16"/>
+      <c r="N10" s="16"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+      <c r="S10" s="7"/>
+      <c r="T10" s="7"/>
+      <c r="U10" s="7"/>
+      <c r="V10" s="7"/>
+      <c r="W10" s="7"/>
+      <c r="X10" s="7"/>
+    </row>
+    <row r="11" spans="1:24">
+      <c r="A11" s="17"/>
+      <c r="B11" s="17"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+      <c r="S11" s="7"/>
+      <c r="T11" s="7"/>
+      <c r="U11" s="7"/>
+      <c r="V11" s="7"/>
+      <c r="W11" s="7"/>
+      <c r="X11" s="7"/>
+    </row>
+    <row r="12" spans="1:24">
+      <c r="A12" s="17"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
+      <c r="W12" s="7"/>
+      <c r="X12" s="7"/>
+    </row>
+    <row r="13" spans="1:24">
+      <c r="A13" s="17"/>
+      <c r="B13" s="17"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
+      <c r="Q13" s="7"/>
+      <c r="R13" s="7"/>
+      <c r="S13" s="7"/>
+      <c r="T13" s="7"/>
+      <c r="U13" s="7"/>
+      <c r="V13" s="7"/>
+      <c r="W13" s="7"/>
+      <c r="X13" s="7"/>
+    </row>
+    <row r="14" spans="1:24">
+      <c r="A14" s="17"/>
+      <c r="B14" s="17"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="16"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
+      <c r="Q14" s="7"/>
+      <c r="R14" s="7"/>
+      <c r="S14" s="7"/>
+      <c r="T14" s="7"/>
+      <c r="U14" s="7"/>
+      <c r="V14" s="7"/>
+      <c r="W14" s="7"/>
+      <c r="X14" s="7"/>
+    </row>
+    <row r="15" spans="1:24">
+      <c r="A15" s="17"/>
+      <c r="B15" s="17"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="16"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
+      <c r="Q15" s="7"/>
+      <c r="R15" s="7"/>
+      <c r="S15" s="7"/>
+      <c r="T15" s="7"/>
+      <c r="U15" s="7"/>
+      <c r="V15" s="7"/>
+      <c r="W15" s="7"/>
+      <c r="X15" s="7"/>
+    </row>
+    <row r="16" spans="1:24">
+      <c r="A16" s="17"/>
+      <c r="B16" s="17"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="16"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
+      <c r="S16" s="7"/>
+      <c r="T16" s="7"/>
+      <c r="U16" s="7"/>
+      <c r="V16" s="7"/>
+      <c r="W16" s="7"/>
+      <c r="X16" s="7"/>
+    </row>
+    <row r="17" spans="1:24">
+      <c r="A17" s="17"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+      <c r="S17" s="7"/>
+      <c r="T17" s="7"/>
+      <c r="U17" s="7"/>
+      <c r="V17" s="7"/>
+      <c r="W17" s="7"/>
+      <c r="X17" s="7"/>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" s="17"/>
+      <c r="B18" s="17"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+      <c r="S18" s="7"/>
+      <c r="T18" s="7"/>
+      <c r="U18" s="7"/>
+      <c r="V18" s="7"/>
+      <c r="W18" s="7"/>
+      <c r="X18" s="7"/>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="17"/>
+      <c r="B19" s="17"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+      <c r="S19" s="7"/>
+      <c r="T19" s="7"/>
+      <c r="U19" s="7"/>
+      <c r="V19" s="7"/>
+      <c r="W19" s="7"/>
+      <c r="X19" s="7"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C2:L2"/>
+    <mergeCell ref="O2:X2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/plan/Plan.xlsx
+++ b/plan/Plan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Course-management\Source\course-management\plan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4168823-4508-4753-9BA4-BEF93AD38454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B2CE71B-1AD7-4FE1-9600-A4363A5F7553}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resource" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="86">
   <si>
     <t>No</t>
   </si>
@@ -233,9 +233,6 @@
     <t>User service</t>
   </si>
   <si>
-    <t>Search</t>
-  </si>
-  <si>
     <t>Common exception</t>
   </si>
   <si>
@@ -260,12 +257,6 @@
     <t>Văn</t>
   </si>
   <si>
-    <t>Detail screen/delete</t>
-  </si>
-  <si>
-    <t>Create/update</t>
-  </si>
-  <si>
     <t>Thái</t>
   </si>
   <si>
@@ -276,6 +267,24 @@
   </si>
   <si>
     <t>Common (message_en/vn, validation)</t>
+  </si>
+  <si>
+    <t>Function name</t>
+  </si>
+  <si>
+    <t>Common service</t>
+  </si>
+  <si>
+    <t>Staff, Teacher, Student</t>
+  </si>
+  <si>
+    <t>Search (API)</t>
+  </si>
+  <si>
+    <t>Create/update (API)</t>
+  </si>
+  <si>
+    <t>Detail screen/delete (API)</t>
   </si>
 </sst>
 </file>
@@ -520,10 +529,10 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1280,32 +1289,32 @@
     </row>
     <row r="2" spans="1:23">
       <c r="A2" s="17"/>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>56</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
       <c r="L2" s="16"/>
       <c r="M2" s="16"/>
-      <c r="N2" s="37" t="s">
+      <c r="N2" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="O2" s="37"/>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
+      <c r="O2" s="38"/>
+      <c r="P2" s="38"/>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
     </row>
     <row r="3" spans="1:23">
       <c r="A3" s="17" t="s">
@@ -1720,123 +1729,130 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B43DE5D9-EEEF-4F18-8F47-33166F5D148C}">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:Y19"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="32.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.33203125" customWidth="1"/>
-    <col min="3" max="11" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" customWidth="1"/>
+    <col min="4" max="12" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:25">
       <c r="A1" s="17"/>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="15" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25">
+      <c r="A2" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
+      <c r="M2" s="38"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q2" s="38"/>
+      <c r="R2" s="38"/>
+      <c r="S2" s="38"/>
+      <c r="T2" s="38"/>
+      <c r="U2" s="38"/>
+      <c r="V2" s="38"/>
+      <c r="W2" s="38"/>
+      <c r="X2" s="38"/>
+      <c r="Y2" s="38"/>
+    </row>
+    <row r="3" spans="1:25">
+      <c r="A3" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" s="17" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="15" t="s">
-        <v>46</v>
-      </c>
-      <c r="P1" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q1" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="R1" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="S1" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="V1" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="W1" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="X1" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37"/>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
-      <c r="H2" s="37"/>
-      <c r="I2" s="37"/>
-      <c r="J2" s="37"/>
-      <c r="K2" s="37"/>
-      <c r="L2" s="37"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="P2" s="37"/>
-      <c r="Q2" s="37"/>
-      <c r="R2" s="37"/>
-      <c r="S2" s="37"/>
-      <c r="T2" s="37"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="37"/>
-      <c r="W2" s="37"/>
-      <c r="X2" s="37"/>
-    </row>
-    <row r="3" spans="1:24">
-      <c r="A3" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C3" s="17"/>
       <c r="D3" s="17"/>
       <c r="E3" s="17"/>
       <c r="F3" s="17"/>
@@ -1846,9 +1862,9 @@
       <c r="J3" s="17"/>
       <c r="K3" s="17"/>
       <c r="L3" s="17"/>
-      <c r="M3" s="16"/>
+      <c r="M3" s="17"/>
       <c r="N3" s="16"/>
-      <c r="O3" s="17"/>
+      <c r="O3" s="16"/>
       <c r="P3" s="17"/>
       <c r="Q3" s="17"/>
       <c r="R3" s="17"/>
@@ -1858,15 +1874,18 @@
       <c r="V3" s="17"/>
       <c r="W3" s="17"/>
       <c r="X3" s="17"/>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="Y3" s="17"/>
+    </row>
+    <row r="4" spans="1:25">
       <c r="A4" s="17" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="17"/>
+        <v>81</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>75</v>
+      </c>
       <c r="D4" s="17"/>
       <c r="E4" s="17"/>
       <c r="F4" s="17"/>
@@ -1876,9 +1895,9 @@
       <c r="J4" s="17"/>
       <c r="K4" s="17"/>
       <c r="L4" s="17"/>
-      <c r="M4" s="16"/>
+      <c r="M4" s="17"/>
       <c r="N4" s="16"/>
-      <c r="O4" s="17"/>
+      <c r="O4" s="16"/>
       <c r="P4" s="17"/>
       <c r="Q4" s="17"/>
       <c r="R4" s="17"/>
@@ -1888,15 +1907,18 @@
       <c r="V4" s="17"/>
       <c r="W4" s="17"/>
       <c r="X4" s="17"/>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="Y4" s="17"/>
+    </row>
+    <row r="5" spans="1:25">
       <c r="A5" s="17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="C5" s="17"/>
+        <v>81</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>71</v>
+      </c>
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
       <c r="F5" s="17"/>
@@ -1906,9 +1928,9 @@
       <c r="J5" s="17"/>
       <c r="K5" s="17"/>
       <c r="L5" s="17"/>
-      <c r="M5" s="16"/>
+      <c r="M5" s="17"/>
       <c r="N5" s="16"/>
-      <c r="O5" s="7"/>
+      <c r="O5" s="16"/>
       <c r="P5" s="7"/>
       <c r="Q5" s="7"/>
       <c r="R5" s="7"/>
@@ -1918,15 +1940,18 @@
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="Y5" s="7"/>
+    </row>
+    <row r="6" spans="1:25">
       <c r="A6" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="17"/>
+      <c r="C6" s="17" t="s">
+        <v>72</v>
+      </c>
       <c r="D6" s="17"/>
       <c r="E6" s="17"/>
       <c r="F6" s="17"/>
@@ -1936,9 +1961,9 @@
       <c r="J6" s="17"/>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
-      <c r="M6" s="16"/>
+      <c r="M6" s="17"/>
       <c r="N6" s="16"/>
-      <c r="O6" s="7"/>
+      <c r="O6" s="16"/>
       <c r="P6" s="7"/>
       <c r="Q6" s="7"/>
       <c r="R6" s="7"/>
@@ -1948,15 +1973,18 @@
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="Y6" s="7"/>
+    </row>
+    <row r="7" spans="1:25">
       <c r="A7" s="17" t="s">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>74</v>
+      </c>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="17"/>
@@ -1966,9 +1994,9 @@
       <c r="J7" s="17"/>
       <c r="K7" s="17"/>
       <c r="L7" s="17"/>
-      <c r="M7" s="16"/>
+      <c r="M7" s="17"/>
       <c r="N7" s="16"/>
-      <c r="O7" s="7"/>
+      <c r="O7" s="16"/>
       <c r="P7" s="7"/>
       <c r="Q7" s="7"/>
       <c r="R7" s="7"/>
@@ -1978,15 +2006,18 @@
       <c r="V7" s="7"/>
       <c r="W7" s="7"/>
       <c r="X7" s="7"/>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="Y7" s="7"/>
+    </row>
+    <row r="8" spans="1:25">
       <c r="A8" s="17" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>73</v>
+      </c>
       <c r="D8" s="17"/>
       <c r="E8" s="17"/>
       <c r="F8" s="17"/>
@@ -1996,9 +2027,9 @@
       <c r="J8" s="17"/>
       <c r="K8" s="17"/>
       <c r="L8" s="17"/>
-      <c r="M8" s="16"/>
+      <c r="M8" s="17"/>
       <c r="N8" s="16"/>
-      <c r="O8" s="7"/>
+      <c r="O8" s="16"/>
       <c r="P8" s="7"/>
       <c r="Q8" s="7"/>
       <c r="R8" s="7"/>
@@ -2008,15 +2039,18 @@
       <c r="V8" s="7"/>
       <c r="W8" s="7"/>
       <c r="X8" s="7"/>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="Y8" s="7"/>
+    </row>
+    <row r="9" spans="1:25">
       <c r="A9" s="17" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="B9" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="17"/>
+        <v>82</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>76</v>
+      </c>
       <c r="D9" s="17"/>
       <c r="E9" s="17"/>
       <c r="F9" s="17"/>
@@ -2026,9 +2060,9 @@
       <c r="J9" s="17"/>
       <c r="K9" s="17"/>
       <c r="L9" s="17"/>
-      <c r="M9" s="16"/>
+      <c r="M9" s="17"/>
       <c r="N9" s="16"/>
-      <c r="O9" s="7"/>
+      <c r="O9" s="16"/>
       <c r="P9" s="7"/>
       <c r="Q9" s="7"/>
       <c r="R9" s="7"/>
@@ -2038,11 +2072,12 @@
       <c r="V9" s="7"/>
       <c r="W9" s="7"/>
       <c r="X9" s="7"/>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="Y9" s="7"/>
+    </row>
+    <row r="10" spans="1:25">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
-      <c r="C10" s="7"/>
+      <c r="C10" s="17"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
@@ -2052,9 +2087,9 @@
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
-      <c r="M10" s="16"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="16"/>
-      <c r="O10" s="7"/>
+      <c r="O10" s="16"/>
       <c r="P10" s="7"/>
       <c r="Q10" s="7"/>
       <c r="R10" s="7"/>
@@ -2064,11 +2099,12 @@
       <c r="V10" s="7"/>
       <c r="W10" s="7"/>
       <c r="X10" s="7"/>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="Y10" s="7"/>
+    </row>
+    <row r="11" spans="1:25">
       <c r="A11" s="17"/>
       <c r="B11" s="17"/>
-      <c r="C11" s="7"/>
+      <c r="C11" s="17"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
@@ -2078,9 +2114,9 @@
       <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="16"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="16"/>
-      <c r="O11" s="7"/>
+      <c r="O11" s="16"/>
       <c r="P11" s="7"/>
       <c r="Q11" s="7"/>
       <c r="R11" s="7"/>
@@ -2090,11 +2126,12 @@
       <c r="V11" s="7"/>
       <c r="W11" s="7"/>
       <c r="X11" s="7"/>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="Y11" s="7"/>
+    </row>
+    <row r="12" spans="1:25">
       <c r="A12" s="17"/>
       <c r="B12" s="17"/>
-      <c r="C12" s="7"/>
+      <c r="C12" s="17"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="F12" s="7"/>
@@ -2104,9 +2141,9 @@
       <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
-      <c r="M12" s="16"/>
+      <c r="M12" s="7"/>
       <c r="N12" s="16"/>
-      <c r="O12" s="7"/>
+      <c r="O12" s="16"/>
       <c r="P12" s="7"/>
       <c r="Q12" s="7"/>
       <c r="R12" s="7"/>
@@ -2116,11 +2153,12 @@
       <c r="V12" s="7"/>
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="Y12" s="7"/>
+    </row>
+    <row r="13" spans="1:25">
       <c r="A13" s="17"/>
       <c r="B13" s="17"/>
-      <c r="C13" s="7"/>
+      <c r="C13" s="17"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
@@ -2130,9 +2168,9 @@
       <c r="J13" s="7"/>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
-      <c r="M13" s="16"/>
+      <c r="M13" s="7"/>
       <c r="N13" s="16"/>
-      <c r="O13" s="7"/>
+      <c r="O13" s="16"/>
       <c r="P13" s="7"/>
       <c r="Q13" s="7"/>
       <c r="R13" s="7"/>
@@ -2142,11 +2180,12 @@
       <c r="V13" s="7"/>
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="Y13" s="7"/>
+    </row>
+    <row r="14" spans="1:25">
       <c r="A14" s="17"/>
       <c r="B14" s="17"/>
-      <c r="C14" s="7"/>
+      <c r="C14" s="17"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="7"/>
@@ -2156,9 +2195,9 @@
       <c r="J14" s="7"/>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
-      <c r="M14" s="16"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="16"/>
-      <c r="O14" s="7"/>
+      <c r="O14" s="16"/>
       <c r="P14" s="7"/>
       <c r="Q14" s="7"/>
       <c r="R14" s="7"/>
@@ -2168,11 +2207,12 @@
       <c r="V14" s="7"/>
       <c r="W14" s="7"/>
       <c r="X14" s="7"/>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="Y14" s="7"/>
+    </row>
+    <row r="15" spans="1:25">
       <c r="A15" s="17"/>
       <c r="B15" s="17"/>
-      <c r="C15" s="7"/>
+      <c r="C15" s="17"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
@@ -2182,9 +2222,9 @@
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="7"/>
-      <c r="M15" s="16"/>
+      <c r="M15" s="7"/>
       <c r="N15" s="16"/>
-      <c r="O15" s="7"/>
+      <c r="O15" s="16"/>
       <c r="P15" s="7"/>
       <c r="Q15" s="7"/>
       <c r="R15" s="7"/>
@@ -2194,11 +2234,12 @@
       <c r="V15" s="7"/>
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="Y15" s="7"/>
+    </row>
+    <row r="16" spans="1:25">
       <c r="A16" s="17"/>
       <c r="B16" s="17"/>
-      <c r="C16" s="7"/>
+      <c r="C16" s="17"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="7"/>
@@ -2208,9 +2249,9 @@
       <c r="J16" s="7"/>
       <c r="K16" s="7"/>
       <c r="L16" s="7"/>
-      <c r="M16" s="16"/>
+      <c r="M16" s="7"/>
       <c r="N16" s="16"/>
-      <c r="O16" s="7"/>
+      <c r="O16" s="16"/>
       <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="R16" s="7"/>
@@ -2220,11 +2261,12 @@
       <c r="V16" s="7"/>
       <c r="W16" s="7"/>
       <c r="X16" s="7"/>
-    </row>
-    <row r="17" spans="1:24">
+      <c r="Y16" s="7"/>
+    </row>
+    <row r="17" spans="1:25">
       <c r="A17" s="17"/>
       <c r="B17" s="17"/>
-      <c r="C17" s="7"/>
+      <c r="C17" s="17"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
@@ -2234,9 +2276,9 @@
       <c r="J17" s="7"/>
       <c r="K17" s="7"/>
       <c r="L17" s="7"/>
-      <c r="M17" s="16"/>
+      <c r="M17" s="7"/>
       <c r="N17" s="16"/>
-      <c r="O17" s="7"/>
+      <c r="O17" s="16"/>
       <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="R17" s="7"/>
@@ -2246,11 +2288,12 @@
       <c r="V17" s="7"/>
       <c r="W17" s="7"/>
       <c r="X17" s="7"/>
-    </row>
-    <row r="18" spans="1:24">
+      <c r="Y17" s="7"/>
+    </row>
+    <row r="18" spans="1:25">
       <c r="A18" s="17"/>
       <c r="B18" s="17"/>
-      <c r="C18" s="7"/>
+      <c r="C18" s="17"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="F18" s="7"/>
@@ -2260,9 +2303,9 @@
       <c r="J18" s="7"/>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="16"/>
+      <c r="M18" s="7"/>
       <c r="N18" s="16"/>
-      <c r="O18" s="7"/>
+      <c r="O18" s="16"/>
       <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="R18" s="7"/>
@@ -2272,11 +2315,12 @@
       <c r="V18" s="7"/>
       <c r="W18" s="7"/>
       <c r="X18" s="7"/>
-    </row>
-    <row r="19" spans="1:24">
+      <c r="Y18" s="7"/>
+    </row>
+    <row r="19" spans="1:25">
       <c r="A19" s="17"/>
       <c r="B19" s="17"/>
-      <c r="C19" s="7"/>
+      <c r="C19" s="17"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="F19" s="7"/>
@@ -2286,9 +2330,9 @@
       <c r="J19" s="7"/>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
-      <c r="M19" s="16"/>
+      <c r="M19" s="7"/>
       <c r="N19" s="16"/>
-      <c r="O19" s="7"/>
+      <c r="O19" s="16"/>
       <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="R19" s="7"/>
@@ -2298,11 +2342,12 @@
       <c r="V19" s="7"/>
       <c r="W19" s="7"/>
       <c r="X19" s="7"/>
+      <c r="Y19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="C2:L2"/>
-    <mergeCell ref="O2:X2"/>
+    <mergeCell ref="D2:M2"/>
+    <mergeCell ref="P2:Y2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
